--- a/research/traditional_assets/database/data/vietnam/vietnam_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/vietnam/vietnam_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.113</v>
+        <v>0.1028</v>
       </c>
       <c r="E2">
-        <v>0.172</v>
+        <v>0.175</v>
       </c>
       <c r="G2">
-        <v>0.09427898007285195</v>
+        <v>0.114865866310953</v>
       </c>
       <c r="H2">
-        <v>0.09427898007285195</v>
+        <v>0.114865866310953</v>
       </c>
       <c r="I2">
-        <v>0.1129205056781658</v>
+        <v>0.05854453831332444</v>
       </c>
       <c r="J2">
-        <v>0.09098322542220072</v>
+        <v>0.05064231188893407</v>
       </c>
       <c r="K2">
-        <v>40.4</v>
+        <v>22.8</v>
       </c>
       <c r="L2">
-        <v>0.0865652453396186</v>
+        <v>0.03379279679857714</v>
       </c>
       <c r="M2">
-        <v>18.373</v>
+        <v>18.0249</v>
       </c>
       <c r="N2">
-        <v>0.0385582371458552</v>
+        <v>0.03439210074413279</v>
       </c>
       <c r="O2">
-        <v>0.4547772277227723</v>
+        <v>0.7905657894736843</v>
       </c>
       <c r="P2">
-        <v>18.37</v>
+        <v>18.0249</v>
       </c>
       <c r="Q2">
-        <v>0.03855194123819518</v>
+        <v>0.03439210074413279</v>
       </c>
       <c r="R2">
-        <v>0.4547029702970297</v>
+        <v>0.7905657894736843</v>
       </c>
       <c r="S2">
-        <v>0.003000000000000114</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.0001632830784303115</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>19.99</v>
+        <v>21.73</v>
       </c>
       <c r="V2">
-        <v>0.04195173137460651</v>
+        <v>0.04146155313871398</v>
       </c>
       <c r="W2">
-        <v>0.1516966067864271</v>
+        <v>0.1326826826826827</v>
       </c>
       <c r="X2">
-        <v>0.07697577764364623</v>
+        <v>0.115746914867459</v>
       </c>
       <c r="Y2">
-        <v>0.0747208291427809</v>
+        <v>0.01693576781522366</v>
       </c>
       <c r="Z2">
-        <v>1.924853584096346</v>
+        <v>2.699015921273702</v>
       </c>
       <c r="AA2">
-        <v>0.1626371261956518</v>
+        <v>0.1806183818550651</v>
       </c>
       <c r="AB2">
-        <v>0.07697577764364623</v>
+        <v>0.115746914867459</v>
       </c>
       <c r="AC2">
-        <v>0.08566134855200559</v>
+        <v>0.06487146698760608</v>
       </c>
       <c r="AD2">
-        <v>10.8</v>
+        <v>15.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>10.8</v>
+        <v>15.2</v>
       </c>
       <c r="AG2">
-        <v>-9.190000000000001</v>
+        <v>-6.530000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.02216293864149395</v>
+        <v>0.02818468384943445</v>
       </c>
       <c r="AI2">
-        <v>0.03774903879762321</v>
+        <v>0.04133804732118575</v>
       </c>
       <c r="AJ2">
-        <v>-0.01966574650660162</v>
+        <v>-0.01261665088780262</v>
       </c>
       <c r="AK2">
-        <v>-0.03453459095862613</v>
+        <v>-0.01887446888458537</v>
       </c>
       <c r="AL2">
-        <v>1.298</v>
+        <v>3.671</v>
       </c>
       <c r="AM2">
-        <v>1.298</v>
+        <v>3.671</v>
       </c>
       <c r="AN2">
-        <v>0.1928571428571429</v>
+        <v>0.355638745905475</v>
       </c>
       <c r="AO2">
-        <v>40.60092449922958</v>
+        <v>10.76001089621357</v>
       </c>
       <c r="AP2">
-        <v>-0.1641071428571429</v>
+        <v>-0.1527842770238652</v>
       </c>
       <c r="AQ2">
-        <v>40.60092449922958</v>
+        <v>10.76001089621357</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Petrolimex Insurance Corporation (HOSE:PGI)</t>
+          <t>Bank for Investment and Development of Vietnam Insurance Joint Stock Corporation (HOSE:BIC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.08109999999999999</v>
+        <v>0.136</v>
       </c>
       <c r="E3">
-        <v>0.22</v>
+        <v>0.185</v>
       </c>
       <c r="G3">
-        <v>0.08584005869405721</v>
+        <v>0.1838790931989924</v>
       </c>
       <c r="H3">
-        <v>0.08584005869405721</v>
+        <v>0.1838790931989924</v>
       </c>
       <c r="I3">
-        <v>0.123991195891416</v>
+        <v>0.1343408900083963</v>
       </c>
       <c r="J3">
-        <v>0.1001057753331923</v>
+        <v>0.1046845048555994</v>
       </c>
       <c r="K3">
-        <v>13.1</v>
+        <v>12.1</v>
       </c>
       <c r="L3">
-        <v>0.09611151870873073</v>
+        <v>0.1015952980688497</v>
       </c>
       <c r="M3">
-        <v>4.55</v>
+        <v>7.3899</v>
       </c>
       <c r="N3">
-        <v>0.03998242530755712</v>
+        <v>0.0560690440060698</v>
       </c>
       <c r="O3">
-        <v>0.3473282442748092</v>
+        <v>0.6107355371900827</v>
       </c>
       <c r="P3">
-        <v>4.55</v>
+        <v>7.3899</v>
       </c>
       <c r="Q3">
-        <v>0.03998242530755712</v>
+        <v>0.0560690440060698</v>
       </c>
       <c r="R3">
-        <v>0.3473282442748092</v>
+        <v>0.6107355371900827</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,31 +770,16 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>5.52</v>
+        <v>3.49</v>
       </c>
       <c r="V3">
-        <v>0.04850615114235501</v>
-      </c>
-      <c r="W3">
-        <v>0.1984848484848485</v>
+        <v>0.02647951441578148</v>
       </c>
       <c r="X3">
-        <v>0.07697577764364623</v>
-      </c>
-      <c r="Y3">
-        <v>0.1215090708412023</v>
-      </c>
-      <c r="Z3">
-        <v>2.302753843554655</v>
-      </c>
-      <c r="AA3">
-        <v>0.2305189589105273</v>
+        <v>0.115746914867459</v>
       </c>
       <c r="AB3">
-        <v>0.07697577764364623</v>
-      </c>
-      <c r="AC3">
-        <v>0.153543181266881</v>
+        <v>0.115746914867459</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -806,7 +791,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-5.52</v>
+        <v>-3.49</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -815,28 +800,28 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.05097894347986701</v>
+        <v>-0.02719975060400592</v>
       </c>
       <c r="AK3">
-        <v>-0.08060747663551401</v>
+        <v>-0.03496643622883479</v>
       </c>
       <c r="AL3">
-        <v>0.87</v>
+        <v>0.005</v>
       </c>
       <c r="AM3">
-        <v>0.87</v>
+        <v>0.005</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>19.42528735632184</v>
+        <v>3200</v>
       </c>
       <c r="AP3">
-        <v>-0.3</v>
+        <v>-0.2141104294478528</v>
       </c>
       <c r="AQ3">
-        <v>19.42528735632184</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bank for Investment and Development of Vietnam Insurance Joint Stock Corporation (HOSE:BIC)</t>
+          <t>Bao Minh Insurance Corporation (HOSE:BMI)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,79 +841,79 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.113</v>
+        <v>0.0796</v>
       </c>
       <c r="E4">
-        <v>0.172</v>
+        <v>0.0483</v>
       </c>
       <c r="G4">
-        <v>0.1631679389312977</v>
+        <v>0.09030948756976155</v>
       </c>
       <c r="H4">
-        <v>0.1631679389312977</v>
+        <v>0.09030948756976155</v>
       </c>
       <c r="I4">
-        <v>0.1908396946564886</v>
+        <v>0.09791983764586505</v>
       </c>
       <c r="J4">
-        <v>0.1486236409900532</v>
+        <v>0.08573269238490487</v>
       </c>
       <c r="K4">
-        <v>15.2</v>
+        <v>12.2</v>
       </c>
       <c r="L4">
-        <v>0.1450381679389313</v>
+        <v>0.06189751395230847</v>
       </c>
       <c r="M4">
-        <v>10.303</v>
+        <v>6.89</v>
       </c>
       <c r="N4">
-        <v>0.06690259740259741</v>
+        <v>0.06959595959595959</v>
       </c>
       <c r="O4">
-        <v>0.6778289473684211</v>
+        <v>0.5647540983606557</v>
       </c>
       <c r="P4">
+        <v>6.89</v>
+      </c>
+      <c r="Q4">
+        <v>0.06959595959595959</v>
+      </c>
+      <c r="R4">
+        <v>0.5647540983606557</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
         <v>10.3</v>
       </c>
-      <c r="Q4">
-        <v>0.06688311688311689</v>
-      </c>
-      <c r="R4">
-        <v>0.6776315789473685</v>
-      </c>
-      <c r="S4">
-        <v>0.003000000000000114</v>
-      </c>
-      <c r="T4">
-        <v>0.0002911773269921492</v>
-      </c>
-      <c r="U4">
-        <v>3.67</v>
-      </c>
       <c r="V4">
-        <v>0.02383116883116883</v>
+        <v>0.104040404040404</v>
       </c>
       <c r="W4">
-        <v>0.1516966067864271</v>
+        <v>0.1221221221221221</v>
       </c>
       <c r="X4">
-        <v>0.07697577764364623</v>
+        <v>0.115746914867459</v>
       </c>
       <c r="Y4">
-        <v>0.0747208291427809</v>
+        <v>0.006375207254663076</v>
       </c>
       <c r="Z4">
-        <v>1.094288399289965</v>
+        <v>2.224604966139955</v>
       </c>
       <c r="AA4">
-        <v>0.1626371261956518</v>
+        <v>0.1907213732400084</v>
       </c>
       <c r="AB4">
-        <v>0.07697577764364623</v>
+        <v>0.115746914867459</v>
       </c>
       <c r="AC4">
-        <v>0.08566134855200559</v>
+        <v>0.0749744583725494</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -940,7 +925,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-3.67</v>
+        <v>-10.3</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -949,22 +934,28 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.02441295815871749</v>
+        <v>-0.1161217587373168</v>
       </c>
       <c r="AK4">
-        <v>-0.03510953793169425</v>
+        <v>-0.1161217587373168</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AN4">
         <v>0</v>
       </c>
+      <c r="AO4">
+        <v>10.72222222222222</v>
+      </c>
       <c r="AP4">
-        <v>-0.1807881773399015</v>
+        <v>-0.515</v>
+      </c>
+      <c r="AQ4">
+        <v>10.72222222222222</v>
       </c>
     </row>
     <row r="5">
@@ -975,130 +966,261 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Petrolimex Insurance Corporation (HOSE:PGI)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.0559</v>
+      </c>
+      <c r="E5">
+        <v>0.175</v>
+      </c>
+      <c r="G5">
+        <v>0.163265306122449</v>
+      </c>
+      <c r="H5">
+        <v>0.163265306122449</v>
+      </c>
+      <c r="I5">
+        <v>0.109599395313681</v>
+      </c>
+      <c r="J5">
+        <v>0.08826072516548705</v>
+      </c>
+      <c r="K5">
+        <v>10.6</v>
+      </c>
+      <c r="L5">
+        <v>0.08012093726379439</v>
+      </c>
+      <c r="M5">
+        <v>3.72</v>
+      </c>
+      <c r="N5">
+        <v>0.02980769230769231</v>
+      </c>
+      <c r="O5">
+        <v>0.3509433962264151</v>
+      </c>
+      <c r="P5">
+        <v>3.72</v>
+      </c>
+      <c r="Q5">
+        <v>0.02980769230769231</v>
+      </c>
+      <c r="R5">
+        <v>0.3509433962264151</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>3.88</v>
+      </c>
+      <c r="V5">
+        <v>0.03108974358974359</v>
+      </c>
+      <c r="W5">
+        <v>0.1432432432432433</v>
+      </c>
+      <c r="X5">
+        <v>0.115746914867459</v>
+      </c>
+      <c r="Y5">
+        <v>0.02749632837578422</v>
+      </c>
+      <c r="Z5">
+        <v>1.931950934579439</v>
+      </c>
+      <c r="AA5">
+        <v>0.1705153904701218</v>
+      </c>
+      <c r="AB5">
+        <v>0.115746914867459</v>
+      </c>
+      <c r="AC5">
+        <v>0.05476847560266276</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>-3.88</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.03208733046642408</v>
+      </c>
+      <c r="AK5">
+        <v>-0.05509798352740698</v>
+      </c>
+      <c r="AL5">
+        <v>1.38</v>
+      </c>
+      <c r="AM5">
+        <v>1.38</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>10.5072463768116</v>
+      </c>
+      <c r="AP5">
+        <v>-0.2395061728395062</v>
+      </c>
+      <c r="AQ5">
+        <v>10.5072463768116</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Post &amp; Telecommunication Joint Stock Insurance Corporation (HNX:PTI)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.13</v>
-      </c>
-      <c r="E5">
-        <v>0.0587</v>
-      </c>
-      <c r="G5">
-        <v>0.0673758865248227</v>
-      </c>
-      <c r="H5">
-        <v>0.0673758865248227</v>
-      </c>
-      <c r="I5">
-        <v>0.07003546099290781</v>
-      </c>
-      <c r="J5">
-        <v>0.0582018831010027</v>
-      </c>
-      <c r="K5">
-        <v>12.1</v>
-      </c>
-      <c r="L5">
-        <v>0.05363475177304965</v>
-      </c>
-      <c r="M5">
-        <v>3.52</v>
-      </c>
-      <c r="N5">
-        <v>0.01686631528509823</v>
-      </c>
-      <c r="O5">
-        <v>0.2909090909090909</v>
-      </c>
-      <c r="P5">
-        <v>3.52</v>
-      </c>
-      <c r="Q5">
-        <v>0.01686631528509823</v>
-      </c>
-      <c r="R5">
-        <v>0.2909090909090909</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>10.8</v>
-      </c>
-      <c r="V5">
-        <v>0.05174892189746048</v>
-      </c>
-      <c r="W5">
-        <v>0.145083932853717</v>
-      </c>
-      <c r="X5">
-        <v>0.07953738147134676</v>
-      </c>
-      <c r="Y5">
-        <v>0.06554655138237026</v>
-      </c>
-      <c r="Z5">
-        <v>2.578285714285714</v>
-      </c>
-      <c r="AA5">
-        <v>0.1500610837438424</v>
-      </c>
-      <c r="AB5">
-        <v>0.07793022304028166</v>
-      </c>
-      <c r="AC5">
-        <v>0.0721308607035607</v>
-      </c>
-      <c r="AD5">
-        <v>10.8</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>10.8</v>
-      </c>
-      <c r="AG5">
-        <v>0</v>
-      </c>
-      <c r="AH5">
-        <v>0.04920273348519363</v>
-      </c>
-      <c r="AI5">
-        <v>0.1039461020211742</v>
-      </c>
-      <c r="AJ5">
-        <v>0</v>
-      </c>
-      <c r="AK5">
-        <v>0</v>
-      </c>
-      <c r="AL5">
-        <v>0.428</v>
-      </c>
-      <c r="AM5">
-        <v>0.428</v>
-      </c>
-      <c r="AN5">
-        <v>0.6242774566473989</v>
-      </c>
-      <c r="AO5">
-        <v>36.91588785046729</v>
-      </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
-      <c r="AQ5">
-        <v>36.91588785046729</v>
+      <c r="D6">
+        <v>0.126</v>
+      </c>
+      <c r="G6">
+        <v>0.07161803713527852</v>
+      </c>
+      <c r="H6">
+        <v>0.07161803713527852</v>
+      </c>
+      <c r="I6">
+        <v>-0.04553492484526968</v>
+      </c>
+      <c r="J6">
+        <v>-0.04553492484526968</v>
+      </c>
+      <c r="K6">
+        <v>-12.1</v>
+      </c>
+      <c r="L6">
+        <v>-0.05349248452696729</v>
+      </c>
+      <c r="M6">
+        <v>0.025</v>
+      </c>
+      <c r="N6">
+        <v>0.0001483679525222552</v>
+      </c>
+      <c r="O6">
+        <v>-0.002066115702479339</v>
+      </c>
+      <c r="P6">
+        <v>0.025</v>
+      </c>
+      <c r="Q6">
+        <v>0.0001483679525222552</v>
+      </c>
+      <c r="R6">
+        <v>-0.002066115702479339</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>4.06</v>
+      </c>
+      <c r="V6">
+        <v>0.02409495548961424</v>
+      </c>
+      <c r="W6">
+        <v>-0.1302475780409042</v>
+      </c>
+      <c r="X6">
+        <v>0.1212998791688733</v>
+      </c>
+      <c r="Y6">
+        <v>-0.2515474572097775</v>
+      </c>
+      <c r="Z6">
+        <v>2.434876210979548</v>
+      </c>
+      <c r="AA6">
+        <v>-0.1108719052744887</v>
+      </c>
+      <c r="AB6">
+        <v>0.1173407519617202</v>
+      </c>
+      <c r="AC6">
+        <v>-0.2282126572362089</v>
+      </c>
+      <c r="AD6">
+        <v>15.2</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>15.2</v>
+      </c>
+      <c r="AG6">
+        <v>11.14</v>
+      </c>
+      <c r="AH6">
+        <v>0.08274360370168754</v>
+      </c>
+      <c r="AI6">
+        <v>0.1668496158068057</v>
+      </c>
+      <c r="AJ6">
+        <v>0.06201291471832555</v>
+      </c>
+      <c r="AK6">
+        <v>0.1279871323529412</v>
+      </c>
+      <c r="AL6">
+        <v>0.486</v>
+      </c>
+      <c r="AM6">
+        <v>0.486</v>
+      </c>
+      <c r="AN6">
+        <v>-1.557377049180328</v>
+      </c>
+      <c r="AO6">
+        <v>-21.19341563786008</v>
+      </c>
+      <c r="AP6">
+        <v>-1.141393442622951</v>
+      </c>
+      <c r="AQ6">
+        <v>-21.19341563786008</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/vietnam/vietnam_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/vietnam/vietnam_insurance_prop_cas.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1028</v>
+        <v>0.0789</v>
       </c>
       <c r="E2">
-        <v>0.175</v>
+        <v>0.1205</v>
       </c>
       <c r="G2">
-        <v>0.114865866310953</v>
+        <v>0.04826227662867594</v>
       </c>
       <c r="H2">
-        <v>0.114865866310953</v>
+        <v>0.04826227662867594</v>
       </c>
       <c r="I2">
-        <v>0.05854453831332444</v>
+        <v>0.08314337976642745</v>
       </c>
       <c r="J2">
-        <v>0.05064231188893407</v>
+        <v>0.06750421065621075</v>
       </c>
       <c r="K2">
-        <v>22.8</v>
+        <v>44.76</v>
       </c>
       <c r="L2">
-        <v>0.03379279679857714</v>
+        <v>0.06298016040523427</v>
       </c>
       <c r="M2">
-        <v>18.0249</v>
+        <v>15.145</v>
       </c>
       <c r="N2">
-        <v>0.03439210074413279</v>
+        <v>0.03322729267222466</v>
       </c>
       <c r="O2">
-        <v>0.7905657894736843</v>
+        <v>0.3383601429848079</v>
       </c>
       <c r="P2">
-        <v>18.0249</v>
+        <v>15.145</v>
       </c>
       <c r="Q2">
-        <v>0.03439210074413279</v>
+        <v>0.03322729267222466</v>
       </c>
       <c r="R2">
-        <v>0.7905657894736843</v>
+        <v>0.3383601429848079</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>21.73</v>
+        <v>22.66</v>
       </c>
       <c r="V2">
-        <v>0.04146155313871398</v>
+        <v>0.04971478718736288</v>
       </c>
       <c r="W2">
-        <v>0.1326826826826827</v>
+        <v>0.1314042171377299</v>
       </c>
       <c r="X2">
-        <v>0.115746914867459</v>
+        <v>0.1007468324086035</v>
       </c>
       <c r="Y2">
-        <v>0.01693576781522366</v>
+        <v>0.03065738472912642</v>
       </c>
       <c r="Z2">
-        <v>2.699015921273702</v>
+        <v>2.069176347279238</v>
       </c>
       <c r="AA2">
-        <v>0.1806183818550651</v>
+        <v>0.1553344119645014</v>
       </c>
       <c r="AB2">
-        <v>0.115746914867459</v>
+        <v>0.09911056307799902</v>
       </c>
       <c r="AC2">
-        <v>0.06487146698760608</v>
+        <v>0.05622384888650242</v>
       </c>
       <c r="AD2">
-        <v>15.2</v>
+        <v>24.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>15.2</v>
+        <v>24.9</v>
       </c>
       <c r="AG2">
-        <v>-6.530000000000001</v>
+        <v>2.239999999999998</v>
       </c>
       <c r="AH2">
-        <v>0.02818468384943445</v>
+        <v>0.05179945912211358</v>
       </c>
       <c r="AI2">
-        <v>0.04133804732118575</v>
+        <v>0.06324612649225299</v>
       </c>
       <c r="AJ2">
-        <v>-0.01261665088780262</v>
+        <v>0.004890402584927077</v>
       </c>
       <c r="AK2">
-        <v>-0.01887446888458537</v>
+        <v>0.006037084950409654</v>
       </c>
       <c r="AL2">
-        <v>3.671</v>
+        <v>1.835</v>
       </c>
       <c r="AM2">
-        <v>3.671</v>
+        <v>1.835</v>
       </c>
       <c r="AN2">
-        <v>0.355638745905475</v>
+        <v>0.3910790010994188</v>
       </c>
       <c r="AO2">
-        <v>10.76001089621357</v>
+        <v>32.20163487738419</v>
       </c>
       <c r="AP2">
-        <v>-0.1527842770238652</v>
+        <v>0.03518140411496778</v>
       </c>
       <c r="AQ2">
-        <v>10.76001089621357</v>
+        <v>32.20163487738419</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bank for Investment and Development of Vietnam Insurance Joint Stock Corporation (HOSE:BIC)</t>
+          <t>Bao Minh Insurance Corporation (HOSE:BMI)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.136</v>
+        <v>0.06709999999999999</v>
       </c>
       <c r="E3">
-        <v>0.185</v>
+        <v>0.125</v>
       </c>
       <c r="G3">
-        <v>0.1838790931989924</v>
+        <v>0.08637873754152824</v>
       </c>
       <c r="H3">
-        <v>0.1838790931989924</v>
+        <v>0.08637873754152824</v>
       </c>
       <c r="I3">
-        <v>0.1343408900083963</v>
+        <v>0.08780256288561937</v>
       </c>
       <c r="J3">
-        <v>0.1046845048555994</v>
+        <v>0.07659618314890217</v>
       </c>
       <c r="K3">
-        <v>12.1</v>
+        <v>13.2</v>
       </c>
       <c r="L3">
-        <v>0.1015952980688497</v>
+        <v>0.06264831514000949</v>
       </c>
       <c r="M3">
-        <v>7.3899</v>
+        <v>2.26</v>
       </c>
       <c r="N3">
-        <v>0.0560690440060698</v>
+        <v>0.02140151515151515</v>
       </c>
       <c r="O3">
-        <v>0.6107355371900827</v>
+        <v>0.1712121212121212</v>
       </c>
       <c r="P3">
-        <v>7.3899</v>
+        <v>2.26</v>
       </c>
       <c r="Q3">
-        <v>0.0560690440060698</v>
+        <v>0.02140151515151515</v>
       </c>
       <c r="R3">
-        <v>0.6107355371900827</v>
+        <v>0.1712121212121212</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,16 +770,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.49</v>
+        <v>8.65</v>
       </c>
       <c r="V3">
-        <v>0.02647951441578148</v>
+        <v>0.0819128787878788</v>
+      </c>
+      <c r="W3">
+        <v>0.1333333333333333</v>
       </c>
       <c r="X3">
-        <v>0.115746914867459</v>
+        <v>0.09823279221829351</v>
+      </c>
+      <c r="Y3">
+        <v>0.03510054111503982</v>
+      </c>
+      <c r="Z3">
+        <v>2.375422773393461</v>
+      </c>
+      <c r="AA3">
+        <v>0.1819483178069187</v>
       </c>
       <c r="AB3">
-        <v>0.115746914867459</v>
+        <v>0.09823279221829351</v>
+      </c>
+      <c r="AC3">
+        <v>0.08371552558862516</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -791,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-3.49</v>
+        <v>-8.65</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -800,28 +815,28 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.02719975060400592</v>
+        <v>-0.08922124806601342</v>
       </c>
       <c r="AK3">
-        <v>-0.03496643622883479</v>
+        <v>-0.08867247565351102</v>
       </c>
       <c r="AL3">
-        <v>0.005</v>
+        <v>0.48</v>
       </c>
       <c r="AM3">
-        <v>0.005</v>
+        <v>0.48</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>3200</v>
+        <v>38.54166666666667</v>
       </c>
       <c r="AP3">
-        <v>-0.2141104294478528</v>
+        <v>-0.4528795811518325</v>
       </c>
       <c r="AQ3">
-        <v>3200</v>
+        <v>38.54166666666667</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bao Minh Insurance Corporation (HOSE:BMI)</t>
+          <t>Bank for Investment and Development of Vietnam Insurance Joint Stock Corporation (HOSE:BIC)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -841,46 +856,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0796</v>
+        <v>0.163</v>
       </c>
       <c r="E4">
-        <v>0.0483</v>
+        <v>0.19</v>
       </c>
       <c r="G4">
-        <v>0.09030948756976155</v>
+        <v>0.1082716879623403</v>
       </c>
       <c r="H4">
-        <v>0.09030948756976155</v>
+        <v>0.1082716879623403</v>
       </c>
       <c r="I4">
-        <v>0.09791983764586505</v>
+        <v>0.1378614660390047</v>
       </c>
       <c r="J4">
-        <v>0.08573269238490487</v>
+        <v>0.112268045549467</v>
       </c>
       <c r="K4">
-        <v>12.2</v>
+        <v>16.8</v>
       </c>
       <c r="L4">
-        <v>0.06189751395230847</v>
+        <v>0.1129791526563551</v>
       </c>
       <c r="M4">
-        <v>6.89</v>
+        <v>7.44</v>
       </c>
       <c r="N4">
-        <v>0.06959595959595959</v>
+        <v>0.06128500823723229</v>
       </c>
       <c r="O4">
-        <v>0.5647540983606557</v>
+        <v>0.4428571428571428</v>
       </c>
       <c r="P4">
-        <v>6.89</v>
+        <v>7.44</v>
       </c>
       <c r="Q4">
-        <v>0.06959595959595959</v>
+        <v>0.06128500823723229</v>
       </c>
       <c r="R4">
-        <v>0.5647540983606557</v>
+        <v>0.4428571428571428</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -889,31 +904,31 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>10.3</v>
+        <v>3.85</v>
       </c>
       <c r="V4">
-        <v>0.104040404040404</v>
+        <v>0.03171334431630972</v>
       </c>
       <c r="W4">
-        <v>0.1221221221221221</v>
+        <v>0.1643835616438356</v>
       </c>
       <c r="X4">
-        <v>0.115746914867459</v>
+        <v>0.09823279221829351</v>
       </c>
       <c r="Y4">
-        <v>0.006375207254663076</v>
+        <v>0.0661507694255421</v>
       </c>
       <c r="Z4">
-        <v>2.224604966139955</v>
+        <v>1.524971797764332</v>
       </c>
       <c r="AA4">
-        <v>0.1907213732400084</v>
+        <v>0.1712056032530586</v>
       </c>
       <c r="AB4">
-        <v>0.115746914867459</v>
+        <v>0.09823279221829351</v>
       </c>
       <c r="AC4">
-        <v>0.0749744583725494</v>
+        <v>0.07297281103476505</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -925,7 +940,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-10.3</v>
+        <v>-3.85</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -934,28 +949,28 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.1161217587373168</v>
+        <v>-0.03275202041684389</v>
       </c>
       <c r="AK4">
-        <v>-0.1161217587373168</v>
+        <v>-0.03710843373493976</v>
       </c>
       <c r="AL4">
-        <v>1.8</v>
+        <v>0.001</v>
       </c>
       <c r="AM4">
-        <v>1.8</v>
+        <v>0.001</v>
       </c>
       <c r="AN4">
         <v>0</v>
       </c>
       <c r="AO4">
-        <v>10.72222222222222</v>
+        <v>20500</v>
       </c>
       <c r="AP4">
-        <v>-0.515</v>
+        <v>-0.1850961538461539</v>
       </c>
       <c r="AQ4">
-        <v>10.72222222222222</v>
+        <v>20500</v>
       </c>
     </row>
     <row r="5">
@@ -975,46 +990,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0559</v>
+        <v>0.0562</v>
       </c>
       <c r="E5">
-        <v>0.175</v>
+        <v>0.116</v>
       </c>
       <c r="G5">
-        <v>0.163265306122449</v>
+        <v>0.09278350515463916</v>
       </c>
       <c r="H5">
-        <v>0.163265306122449</v>
+        <v>0.09278350515463916</v>
       </c>
       <c r="I5">
-        <v>0.109599395313681</v>
+        <v>0.08983799705449189</v>
       </c>
       <c r="J5">
-        <v>0.08826072516548705</v>
+        <v>0.07231958762886598</v>
       </c>
       <c r="K5">
-        <v>10.6</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="L5">
-        <v>0.08012093726379439</v>
+        <v>0.07083946980854196</v>
       </c>
       <c r="M5">
-        <v>3.72</v>
+        <v>5.4</v>
       </c>
       <c r="N5">
-        <v>0.02980769230769231</v>
+        <v>0.05009276437847867</v>
       </c>
       <c r="O5">
-        <v>0.3509433962264151</v>
+        <v>0.5613305613305614</v>
       </c>
       <c r="P5">
-        <v>3.72</v>
+        <v>5.4</v>
       </c>
       <c r="Q5">
-        <v>0.02980769230769231</v>
+        <v>0.05009276437847867</v>
       </c>
       <c r="R5">
-        <v>0.3509433962264151</v>
+        <v>0.5613305613305614</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1023,73 +1038,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>3.88</v>
+        <v>7.82</v>
       </c>
       <c r="V5">
-        <v>0.03108974358974359</v>
+        <v>0.0725417439703154</v>
       </c>
       <c r="W5">
-        <v>0.1432432432432433</v>
+        <v>0.1294751009421265</v>
       </c>
       <c r="X5">
-        <v>0.115746914867459</v>
+        <v>0.1032608725989135</v>
       </c>
       <c r="Y5">
-        <v>0.02749632837578422</v>
+        <v>0.02621422834321299</v>
       </c>
       <c r="Z5">
-        <v>1.931950934579439</v>
+        <v>1.928429423459245</v>
       </c>
       <c r="AA5">
-        <v>0.1705153904701218</v>
+        <v>0.1394632206759443</v>
       </c>
       <c r="AB5">
-        <v>0.115746914867459</v>
+        <v>0.09998833393770454</v>
       </c>
       <c r="AC5">
-        <v>0.05476847560266276</v>
+        <v>0.03947488673823979</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="AG5">
-        <v>-3.88</v>
+        <v>3.58</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.09563758389261745</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>0.1314878892733564</v>
       </c>
       <c r="AJ5">
-        <v>-0.03208733046642408</v>
+        <v>0.03214221583767284</v>
       </c>
       <c r="AK5">
-        <v>-0.05509798352740698</v>
+        <v>0.04538539553752536</v>
       </c>
       <c r="AL5">
-        <v>1.38</v>
+        <v>0.626</v>
       </c>
       <c r="AM5">
-        <v>1.38</v>
+        <v>0.626</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>0.7651006711409396</v>
       </c>
       <c r="AO5">
-        <v>10.5072463768116</v>
+        <v>19.4888178913738</v>
       </c>
       <c r="AP5">
-        <v>-0.2395061728395062</v>
+        <v>0.2402684563758389</v>
       </c>
       <c r="AQ5">
-        <v>10.5072463768116</v>
+        <v>19.4888178913738</v>
       </c>
     </row>
     <row r="6">
@@ -1109,43 +1124,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.126</v>
+        <v>0.0907</v>
+      </c>
+      <c r="E6">
+        <v>0.00296</v>
       </c>
       <c r="G6">
-        <v>0.07161803713527852</v>
+        <v>-0.05846867749419953</v>
       </c>
       <c r="H6">
-        <v>0.07161803713527852</v>
+        <v>-0.05846867749419953</v>
       </c>
       <c r="I6">
-        <v>-0.04553492484526968</v>
+        <v>0.03661252900232018</v>
       </c>
       <c r="J6">
-        <v>-0.04553492484526968</v>
+        <v>0.02767476456940084</v>
       </c>
       <c r="K6">
-        <v>-12.1</v>
+        <v>5.14</v>
       </c>
       <c r="L6">
-        <v>-0.05349248452696729</v>
+        <v>0.02385150812064965</v>
       </c>
       <c r="M6">
-        <v>0.025</v>
+        <v>0.045</v>
       </c>
       <c r="N6">
-        <v>0.0001483679525222552</v>
+        <v>0.000371900826446281</v>
       </c>
       <c r="O6">
-        <v>-0.002066115702479339</v>
+        <v>0.008754863813229572</v>
       </c>
       <c r="P6">
-        <v>0.025</v>
+        <v>0.045</v>
       </c>
       <c r="Q6">
-        <v>0.0001483679525222552</v>
+        <v>0.000371900826446281</v>
       </c>
       <c r="R6">
-        <v>-0.002066115702479339</v>
+        <v>0.008754863813229572</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1154,73 +1172,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>4.06</v>
+        <v>2.34</v>
       </c>
       <c r="V6">
-        <v>0.02409495548961424</v>
+        <v>0.01933884297520661</v>
       </c>
       <c r="W6">
-        <v>-0.1302475780409042</v>
+        <v>0.0678996036988111</v>
       </c>
       <c r="X6">
-        <v>0.1212998791688733</v>
+        <v>0.1035375373088519</v>
       </c>
       <c r="Y6">
-        <v>-0.2515474572097775</v>
+        <v>-0.03563793361004083</v>
       </c>
       <c r="Z6">
-        <v>2.434876210979548</v>
+        <v>2.481575310916628</v>
       </c>
       <c r="AA6">
-        <v>-0.1108719052744887</v>
+        <v>0.06867701249085539</v>
       </c>
       <c r="AB6">
-        <v>0.1173407519617202</v>
+        <v>0.100075235141972</v>
       </c>
       <c r="AC6">
-        <v>-0.2282126572362089</v>
+        <v>-0.03139822265111661</v>
       </c>
       <c r="AD6">
-        <v>15.2</v>
+        <v>13.5</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>15.2</v>
+        <v>13.5</v>
       </c>
       <c r="AG6">
-        <v>11.14</v>
+        <v>11.16</v>
       </c>
       <c r="AH6">
-        <v>0.08274360370168754</v>
+        <v>0.1003717472118959</v>
       </c>
       <c r="AI6">
-        <v>0.1668496158068057</v>
+        <v>0.1448497854077253</v>
       </c>
       <c r="AJ6">
-        <v>0.06201291471832555</v>
+        <v>0.08444309927360776</v>
       </c>
       <c r="AK6">
-        <v>0.1279871323529412</v>
+        <v>0.1228263262161567</v>
       </c>
       <c r="AL6">
-        <v>0.486</v>
+        <v>0.728</v>
       </c>
       <c r="AM6">
-        <v>0.486</v>
+        <v>0.728</v>
       </c>
       <c r="AN6">
-        <v>-1.557377049180328</v>
+        <v>1.521984216459978</v>
       </c>
       <c r="AO6">
-        <v>-21.19341563786008</v>
+        <v>10.83791208791209</v>
       </c>
       <c r="AP6">
-        <v>-1.141393442622951</v>
+        <v>1.258173618940248</v>
       </c>
       <c r="AQ6">
-        <v>-21.19341563786008</v>
+        <v>10.83791208791209</v>
       </c>
     </row>
   </sheetData>
